--- a/stories/arbres/TREE-COL-010.xlsx
+++ b/stories/arbres/TREE-COL-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Léa est avec maman, au marché. Léa a envie de jouer. maman est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Léa écoute maman. Léa entend les mots : attendre, puis parler.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le matin. La couverture est douce. maman sourit. Ici, c'est le matin. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers le matin. La couverture est douce. maman sourit. Ici, c'est le matin. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le matin. La couverture est douce. maman sourit. Ici, c'est le matin. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la cuisine. Ça sent le pain chaud. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le matin, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le matin, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le jardin. Le vent est doux. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le matin, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le matin, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le matin, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la chambre. Le sol est un peu froid. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. La lumière est claire. On rit un peu. Cette fin-là est celle de le matin, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le matin, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers après la sieste. On entend un oiseau. maman sourit. Ici, c'est après la sieste. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers après la sieste. On entend un oiseau. maman sourit. Ici, c'est après la sieste. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers après la sieste. On entend un oiseau. maman sourit. Ici, c'est après la sieste. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la cuisine. Une feuille tombe. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de après la sieste, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de après la sieste, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. La lumière est claire. On se tient la main. Cette fin-là est celle de après la sieste, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le jardin. L'eau coule, tout petit bruit. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de après la sieste, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. La lumière est claire. On se tait une seconde. Cette fin-là est celle de après la sieste, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de après la sieste, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la chambre. Un vélo passe au loin. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. La lumière est claire. On rit un peu. Cette fin-là est celle de après la sieste, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de après la sieste, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de après la sieste, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le soir. Ça sent le pain chaud. maman sourit. Ici, c'est le soir. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers le soir. Ça sent le pain chaud. maman sourit. Ici, c'est le soir. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le soir. Ça sent le pain chaud. maman sourit. Ici, c'est le soir. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la cuisine. La lumière est claire. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le soir, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. La lumière est claire. On se tient la main. Cette fin-là est celle de le soir, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le soir, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le jardin. Il y a des miettes sur la table. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le soir, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le soir, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le soir, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi la chambre. Un chat miaule une fois. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le ballon. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le soir, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le seau. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le soir, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le doudou. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le soir, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-010.xlsx
+++ b/stories/arbres/TREE-COL-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Léa est avec maman, au marché. Léa a envie de jouer. maman est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Léa écoute maman. Léa entend les mots : attendre, puis parler.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Léa a choisi la cuisine. Ça sent le pain chaud. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Léa rejoint le ballon. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Léa rejoint le seau. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le matin, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Léa rejoint le doudou. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le matin, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Léa a choisi le jardin. Le vent est doux. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Léa rejoint le ballon. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le matin, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Léa rejoint le seau. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le matin, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Léa rejoint le doudou. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le matin, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Léa a choisi la chambre. Le sol est un peu froid. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Léa rejoint le seau. La lumière est claire. On rit un peu. Cette fin-là est celle de le matin, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le matin, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Léa a choisi la cuisine. Une feuille tombe. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Léa rejoint le ballon. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de après la sieste, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Léa rejoint le seau. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de après la sieste, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Léa rejoint le doudou. La lumière est claire. On se tient la main. Cette fin-là est celle de après la sieste, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Léa a choisi le jardin. L'eau coule, tout petit bruit. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de après la sieste, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Léa rejoint le seau. La lumière est claire. On se tait une seconde. Cette fin-là est celle de après la sieste, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de après la sieste, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Léa a choisi la chambre. Un vélo passe au loin. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Léa rejoint le ballon. La lumière est claire. On rit un peu. Cette fin-là est celle de après la sieste, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Léa rejoint le seau. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de après la sieste, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Léa rejoint le doudou. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de après la sieste, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Tour de parole.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Léa a choisi la cuisine. La lumière est claire. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le soir, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Léa rejoint le seau. La lumière est claire. On se tient la main. Cette fin-là est celle de le soir, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le soir, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Léa a choisi le jardin. Il y a des miettes sur la table. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Léa rejoint le ballon. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le soir, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Léa rejoint le seau. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le soir, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Léa rejoint le doudou. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le soir, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Léa a choisi la chambre. Un chat miaule une fois. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Léa rejoint le ballon. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le soir, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Léa rejoint le seau. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le soir, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Léa rejoint le doudou. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le soir, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-010.xlsx
+++ b/stories/arbres/TREE-COL-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tour de parole — au marché</t>
+          <t>La balance et les oranges de Mila</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La balance du marché fait clic. Mila lève la main. Elle attend. Puis elle parle, pour une orange.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Léa est avec maman, au marché. Léa a envie de jouer. maman est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Léa écoute maman. Léa entend les mots : attendre, puis parler.</t>
+          <t>La bâche du stand claque, tout doux. Les oranges brillent, toutes rondes. La balance fait clic. Les pavés sont encore froids. Le panier de maman est vide. Il gratte un peu, contre le bras. Les pièces de papa tintent. Ça sent le thym. Ça sent la fraise aussi. Un pigeon picore une miette. Tu as tes mains au chaud ? Oui, maman. Le marché parle, tout bas. On écoute d'abord. On lève la main. On attend. Puis on parle. En ce moment, Mila tient le panier. Elle veut une orange. Une orange. On lève la main, Mila. Mila lève la main. Elle attend. La marchande parle encore. Mila attend encore. C'est ton tour. Une orange, s'il te plaît. Bravo. Tu as attendu. Puis tu as parlé. L'orange est froide, un peu lisse. Merci. Tu as fait du bon travail. Le matin, le marché est pâle. Après la sieste, il est calme. Le soir, les lampes s'allument. Tu es prête ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Léa est avec maman, au marché. Léa a envie de jouer. maman est là, tout près. On va apprendre : Tour de parole. Voici le geste : lever la main ; attendre. Léa écoute maman. Léa entend les mots : attendre, puis parler.</t>
+          <t>narrateur|La bâche du stand claque, tout doux.
+narrateur|Les oranges brillent, toutes rondes.
+narrateur|La balance fait clic.
+narrateur|Les pavés sont encore froids.
+narrateur|Le panier de maman est vide.
+narrateur|Il gratte un peu, contre le bras.
+narrateur|Les pièces de papa tintent.
+narrateur|Ça sent le thym.
+narrateur|Ça sent la fraise aussi.
+narrateur|Un pigeon picore une miette.
+maman|Tu as tes mains au chaud ?
+enfant-f|Oui, maman.
+papa|Le marché parle, tout bas.
+maman|On écoute d'abord.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|En ce moment, Mila tient le panier.
+narrateur|Elle veut une orange.
+enfant-f|Une orange.
+maman|On lève la main, Mila.
+narrateur|Mila lève la main.
+narrateur|Elle attend.
+narrateur|La marchande parle encore.
+narrateur|Mila attend encore.
+papa|C'est ton tour.
+enfant-f|Une orange, s'il te plaît.
+maman|Bravo. Tu as attendu.
+papa|Puis tu as parlé.
+narrateur|L'orange est froide, un peu lisse.
+enfant-f|Merci.
+papa|Tu as fait du bon travail.
+narrateur|Le matin, le marché est pâle.
+narrateur|Après la sieste, il est calme.
+narrateur|Le soir, les lampes s'allument.
+maman|Tu es prête ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On va au marché quand ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1565,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On va au marché quand ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le matin. La couverture est douce. maman sourit. Ici, c'est le matin. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>C'est le matin, au marché. La lumière est pâle, un peu bleue. Les caisses sont encore humides. Mila marche près de maman. Elle veut parler. Elle lève la main. Elle attend. J'écoute les cerises d'abord. Puis c'est ton tour, Mila. Les cerises sont rouges. Bravo. Tu as attendu. Puis tu as parlé. Le panier se remplit, tout doux. On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,8 +1734,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa va vers le matin. La couverture est douce. maman sourit. Ici, c'est le matin. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On montre du doigt, sans courir.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|C'est le matin, au marché.
+narrateur|La lumière est pâle, un peu bleue.
+narrateur|Les caisses sont encore humides.
+narrateur|Mila marche près de maman.
+narrateur|Elle veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|J'écoute les cerises d'abord.
+maman|Puis c'est ton tour, Mila.
+enfant-f|Les cerises sont rouges.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Le panier se remplit, tout doux.
+papa|On lève la main. On attend.
+enfant-f|Puis on parle.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>Mila veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1932,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|Mila veut parler.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+          <t>Oui. Elle lève la main. Elle attend. Mila respire, tout calme. Bravo, Mila. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2105,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+maman|Elle lève la main.
+papa|Elle attend.
+narrateur|Mila respire, tout calme.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+enfant-f|Merci, papa.
+maman|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2140,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>On rentre où, maintenant ? La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2304,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|On rentre où, maintenant ?
+papa|La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2333,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi la cuisine. Ça sent le pain chaud. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+          <t>Mila a choisi la cuisine, le matin. Ça sent le pain chaud. La table est un peu farinée. Mila veut parler. Elle lève la main. Elle attend. Je parle du pain d'abord. Puis c'est toi, Mila. Le pain est chaud. Bravo. Tu as attendu. Puis tu as parlé. Une miette brille sur le bois. On lève la main, même à table. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,7 +2473,20 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi la cuisine. Ça sent le pain chaud. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi la cuisine, le matin.
+narrateur|Ça sent le pain chaud.
+narrateur|La table est un peu farinée.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|Je parle du pain d'abord.
+maman|Puis c'est toi, Mila.
+enfant-f|Le pain est chaud.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Une miette brille sur le bois.
+papa|On lève la main, même à table.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2430,7 +2514,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2594,7 +2678,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2622,7 +2707,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon roule vers la table, tout doux. Une miette de pain l'arrête. Mila rejoint le ballon. On est dans la cuisine, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2762,7 +2847,24 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon roule vers la table, tout doux.
+narrateur|Une miette de pain l'arrête.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans la cuisine, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2790,7 +2892,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu la cuisine. Elle a pris le ballon. L'orange brille encore, près du ballon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2930,7 +3032,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le ballon.
+narrateur|L'orange brille encore, près du ballon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2958,7 +3068,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le matin, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau pose près de l'évier. L'eau fait un tout petit bruit. Mila rejoint le seau. On est dans la cuisine, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3098,7 +3208,24 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le matin, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau pose près de l'évier.
+narrateur|L'eau fait un tout petit bruit.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans la cuisine, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3126,7 +3253,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu la cuisine. Elle a pris le seau. Une goutte sèche sur le bord du seau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3266,7 +3393,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le seau.
+narrateur|Une goutte sèche sur le bord du seau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3294,7 +3429,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le matin, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou s'assoit sur la chaise. Ça sent encore le pain. Mila rejoint le doudou. On est dans la cuisine, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3434,7 +3569,24 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le matin, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou s'assoit sur la chaise.
+narrateur|Ça sent encore le pain.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans la cuisine, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3462,7 +3614,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu la cuisine. Elle a pris le doudou. Le doudou a gardé l'odeur du thym. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3602,7 +3754,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le doudou.
+narrateur|Le doudou a gardé l'odeur du thym.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3630,7 +3790,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le jardin. Le vent est doux. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+          <t>Mila a choisi le jardin, le matin. Le vent est doux, un peu frais. Une feuille tourne, tout lent. Mila veut parler. Elle lève la main. Elle attend. Je parle du vent d'abord. Ensuite, c'est toi. La feuille tourne. Bravo, Mila. Tu as attendu. Puis parlé. L'herbe est un peu mouillée. On lève la main, même dehors. Puis on parle.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3770,7 +3930,20 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi le jardin. Le vent est doux. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi le jardin, le matin.
+narrateur|Le vent est doux, un peu frais.
+narrateur|Une feuille tourne, tout lent.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maman|Je parle du vent d'abord.
+papa|Ensuite, c'est toi.
+enfant-f|La feuille tourne.
+maman|Bravo, Mila.
+papa|Tu as attendu. Puis parlé.
+narrateur|L'herbe est un peu mouillée.
+maman|On lève la main, même dehors.
+enfant-f|Puis on parle.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3798,7 +3971,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3962,7 +4135,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3990,7 +4164,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le matin, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon glisse dans l'herbe froide. Une goutte d'eau brille dessus. Mila rejoint le ballon. On est dans le jardin, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4130,7 +4304,24 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le matin, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon glisse dans l'herbe froide.
+narrateur|Une goutte d'eau brille dessus.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans le jardin, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4158,7 +4349,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu le jardin. Elle a pris le ballon. L'herbe a un creux, tout rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4298,7 +4489,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le ballon.
+narrateur|L'herbe a un creux, tout rond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4326,7 +4525,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le matin, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau attend près du bac. Le vent pousse une feuille dedans. Mila rejoint le seau. On est dans le jardin, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4466,7 +4665,24 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le matin, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau attend près du bac.
+narrateur|Le vent pousse une feuille dedans.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans le jardin, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4494,7 +4710,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu le jardin. Elle a pris le seau. Le seau a une feuille collée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4634,7 +4850,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le seau.
+narrateur|Le seau a une feuille collée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4662,7 +4886,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le matin, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou a un peu d'herbe au pied. Le jardin sent la terre mouillée. Mila rejoint le doudou. On est dans le jardin, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4802,7 +5026,24 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le matin, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou a un peu d'herbe au pied.
+narrateur|Le jardin sent la terre mouillée.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans le jardin, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4830,7 +5071,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu le jardin. Elle a pris le doudou. Le doudou a un brin d'herbe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4970,7 +5211,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le doudou.
+narrateur|Le doudou a un brin d'herbe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4998,7 +5247,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi la chambre. Le sol est un peu froid. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+          <t>Mila a choisi la chambre, le matin. Le plaid est doux, tout chaud. La lampe fait un rond jaune. Mila veut parler. Elle lève la main. Elle attend. Je parle de la lampe d'abord. Puis c'est ton tour. Le plaid est doux. Bravo. Tu as attendu. Puis tu as parlé. Le doudou attend sur l'oreiller. On lève la main, même ici. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5138,7 +5387,20 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi la chambre. Le sol est un peu froid. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi la chambre, le matin.
+narrateur|Le plaid est doux, tout chaud.
+narrateur|La lampe fait un rond jaune.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|Je parle de la lampe d'abord.
+maman|Puis c'est ton tour.
+enfant-f|Le plaid est doux.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Le doudou attend sur l'oreiller.
+papa|On lève la main, même ici.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5166,7 +5428,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5330,7 +5592,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5358,7 +5621,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon dort sous le lit. Un rayon touche sa rondeur. Mila rejoint le ballon. On est dans la chambre, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5498,7 +5761,24 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le matin, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon dort sous le lit.
+narrateur|Un rayon touche sa rondeur.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans la chambre, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5526,7 +5806,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu la chambre. Elle a pris le ballon. Le ballon dort, sous le lit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5666,7 +5946,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le ballon.
+narrateur|Le ballon dort, sous le lit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5694,7 +5982,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. La lumière est claire. On rit un peu. Cette fin-là est celle de le matin, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau est près de la commode. Il est vide, tout calme. Mila rejoint le seau. On est dans la chambre, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5834,7 +6122,24 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. La lumière est claire. On rit un peu. Cette fin-là est celle de le matin, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau est près de la commode.
+narrateur|Il est vide, tout calme.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans la chambre, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5862,7 +6167,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu la chambre. Elle a pris le seau. Le seau est rentré, tout vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6002,7 +6307,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le seau.
+narrateur|Le seau est rentré, tout vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6030,7 +6343,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le matin, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou est déjà sur l'oreiller. Le plaid le recouvre, tout doux. Mila rejoint le doudou. On est dans la chambre, le matin. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6170,7 +6483,24 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le matin, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou est déjà sur l'oreiller.
+narrateur|Le plaid le recouvre, tout doux.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans la chambre, le matin.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6198,7 +6528,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le matin. Elle a vu la chambre. Elle a pris le doudou. Le doudou est chaud, sous le plaid. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6338,7 +6668,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le matin.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le doudou.
+narrateur|Le doudou est chaud, sous le plaid.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6366,7 +6704,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers après la sieste. On entend un oiseau. maman sourit. Ici, c'est après la sieste. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On rit un peu. Je suis là. On reste ensemble.</t>
+          <t>C'est après la sieste. Le marché est calme, un peu chaud. La bâche fait de l'ombre. Mila tient encore son doudou. Elle veut une fraise. Elle lève la main. Elle attend. J'écoute le pain d'abord. Ensuite, c'est toi. Une fraise, s'il te plaît. Bravo, Mila. Tu as attendu. Puis parlé. La fraise est tiède, tout douce. On lève la main. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6506,8 +6844,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Léa va vers après la sieste. On entend un oiseau. maman sourit. Ici, c'est après la sieste. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On rit un peu.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Le marché est calme, un peu chaud.
+narrateur|La bâche fait de l'ombre.
+narrateur|Mila tient encore son doudou.
+narrateur|Elle veut une fraise.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maman|J'écoute le pain d'abord.
+papa|Ensuite, c'est toi.
+enfant-f|Une fraise, s'il te plaît.
+maman|Bravo, Mila.
+papa|Tu as attendu. Puis parlé.
+narrateur|La fraise est tiède, tout douce.
+maman|On lève la main.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6535,7 +6886,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>On lève quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6691,7 +7042,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|On lève quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6719,7 +7070,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+          <t>Oui. La main. On lève la main. On attend. Mila lève encore la main. Bravo. Puis tu parles. J'attends. C'est ça.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6863,7 +7214,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+papa|La main.
+maman|On lève la main. On attend.
+narrateur|Mila lève encore la main.
+papa|Bravo.
+maman|Puis tu parles.
+enfant-f|J'attends.
+papa|C'est ça.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6891,7 +7249,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>On rentre où, maintenant ? La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7055,7 +7413,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|On rentre où, maintenant ?
+papa|La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7083,7 +7442,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi la cuisine. Une feuille tombe. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+          <t>Mila a choisi la cuisine, après la sieste. Ça sent le pain chaud. La table est un peu farinée. Mila veut parler. Elle lève la main. Elle attend. Je parle du pain d'abord. Puis c'est toi, Mila. Le pain est chaud. Bravo. Tu as attendu. Puis tu as parlé. Une miette brille sur le bois. On lève la main, même à table. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7223,7 +7582,20 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi la cuisine. Une feuille tombe. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi la cuisine, après la sieste.
+narrateur|Ça sent le pain chaud.
+narrateur|La table est un peu farinée.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|Je parle du pain d'abord.
+maman|Puis c'est toi, Mila.
+enfant-f|Le pain est chaud.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Une miette brille sur le bois.
+papa|On lève la main, même à table.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7251,7 +7623,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7415,7 +7787,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7443,7 +7816,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de après la sieste, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon est tiède, après la sieste. Il roule vers la miette. Mila rejoint le ballon. On est dans la cuisine, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7583,7 +7956,24 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de après la sieste, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon est tiède, après la sieste.
+narrateur|Il roule vers la miette.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans la cuisine, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7611,7 +8001,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu la cuisine. Elle a pris le ballon. Le pain a tiédi, près du ballon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7751,7 +8141,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le ballon.
+narrateur|Le pain a tiédi, près du ballon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7779,7 +8177,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de après la sieste, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau a gardé un peu d'eau. La cuisine est encore calme. Mila rejoint le seau. On est dans la cuisine, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7919,7 +8317,24 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de après la sieste, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau a gardé un peu d'eau.
+narrateur|La cuisine est encore calme.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans la cuisine, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7947,7 +8362,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu la cuisine. Elle a pris le seau. Le seau a un fond d'eau, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8087,7 +8502,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le seau.
+narrateur|Le seau a un fond d'eau, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8115,7 +8538,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. La lumière est claire. On se tient la main. Cette fin-là est celle de après la sieste, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou sent le pain chaud. Il a un pli, après la sieste. Mila rejoint le doudou. On est dans la cuisine, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8255,7 +8678,24 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. La lumière est claire. On se tient la main. Cette fin-là est celle de après la sieste, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou sent le pain chaud.
+narrateur|Il a un pli, après la sieste.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans la cuisine, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8283,7 +8723,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu la cuisine. Elle a pris le doudou. Le doudou a un pli de sieste. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8423,7 +8863,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le doudou.
+narrateur|Le doudou a un pli de sieste.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8451,7 +8899,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le jardin. L'eau coule, tout petit bruit. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+          <t>Mila a choisi le jardin, après la sieste. Le vent est doux, un peu frais. Une feuille tourne, tout lent. Mila veut parler. Elle lève la main. Elle attend. Je parle du vent d'abord. Ensuite, c'est toi. La feuille tourne. Bravo, Mila. Tu as attendu. Puis parlé. L'herbe est un peu mouillée. On lève la main, même dehors. Puis on parle.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8591,7 +9039,20 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi le jardin. L'eau coule, tout petit bruit. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi le jardin, après la sieste.
+narrateur|Le vent est doux, un peu frais.
+narrateur|Une feuille tourne, tout lent.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maman|Je parle du vent d'abord.
+papa|Ensuite, c'est toi.
+enfant-f|La feuille tourne.
+maman|Bravo, Mila.
+papa|Tu as attendu. Puis parlé.
+narrateur|L'herbe est un peu mouillée.
+maman|On lève la main, même dehors.
+enfant-f|Puis on parle.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8619,7 +9080,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8783,7 +9244,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8811,7 +9273,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de après la sieste, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon rebondit, tout bas, dans l'herbe. L'ombre de la bâche n'est plus là. Mila rejoint le ballon. On est dans le jardin, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8951,7 +9413,24 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de après la sieste, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon rebondit, tout bas, dans l'herbe.
+narrateur|L'ombre de la bâche n'est plus là.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans le jardin, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8979,7 +9458,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu le jardin. Elle a pris le ballon. Le ballon a une tache d'herbe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9119,7 +9598,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le ballon.
+narrateur|Le ballon a une tache d'herbe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9147,7 +9634,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. La lumière est claire. On se tait une seconde. Cette fin-là est celle de après la sieste, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau est chaud, au soleil. Une abeille passe, tout loin. Mila rejoint le seau. On est dans le jardin, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9287,7 +9774,24 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. La lumière est claire. On se tait une seconde. Cette fin-là est celle de après la sieste, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau est chaud, au soleil.
+narrateur|Une abeille passe, tout loin.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans le jardin, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9315,7 +9819,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu le jardin. Elle a pris le seau. Le seau sent encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9455,7 +9959,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le seau.
+narrateur|Le seau sent encore le soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9483,7 +9995,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de après la sieste, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou sèche un peu, dehors. Une feuille s'y pose, tout léger. Mila rejoint le doudou. On est dans le jardin, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9623,7 +10135,24 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de après la sieste, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou sèche un peu, dehors.
+narrateur|Une feuille s'y pose, tout léger.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans le jardin, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9651,7 +10180,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu le jardin. Elle a pris le doudou. Une feuille reste sur le doudou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9791,7 +10320,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le doudou.
+narrateur|Une feuille reste sur le doudou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9819,7 +10356,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi la chambre. Un vélo passe au loin. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+          <t>Mila a choisi la chambre, après la sieste. Le plaid est doux, tout chaud. La lampe fait un rond jaune. Mila veut parler. Elle lève la main. Elle attend. Je parle de la lampe d'abord. Puis c'est ton tour. Le plaid est doux. Bravo. Tu as attendu. Puis tu as parlé. Le doudou attend sur l'oreiller. On lève la main, même ici. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9959,7 +10496,20 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi la chambre. Un vélo passe au loin. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi la chambre, après la sieste.
+narrateur|Le plaid est doux, tout chaud.
+narrateur|La lampe fait un rond jaune.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|Je parle de la lampe d'abord.
+maman|Puis c'est ton tour.
+enfant-f|Le plaid est doux.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Le doudou attend sur l'oreiller.
+papa|On lève la main, même ici.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9987,7 +10537,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10151,7 +10701,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10179,7 +10730,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. La lumière est claire. On rit un peu. Cette fin-là est celle de après la sieste, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon a une marque d'oreiller. La chambre est encore un peu sombre. Mila rejoint le ballon. On est dans la chambre, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10319,7 +10870,24 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. La lumière est claire. On rit un peu. Cette fin-là est celle de après la sieste, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon a une marque d'oreiller.
+narrateur|La chambre est encore un peu sombre.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans la chambre, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10347,7 +10915,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu la chambre. Elle a pris le ballon. Le ballon a un rond d'oreiller. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10487,7 +11055,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le ballon.
+narrateur|Le ballon a un rond d'oreiller.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10515,7 +11091,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de après la sieste, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau attend au pied du lit. Le volet est à moitié ouvert. Mila rejoint le seau. On est dans la chambre, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10655,7 +11231,24 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de après la sieste, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau attend au pied du lit.
+narrateur|Le volet est à moitié ouvert.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans la chambre, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10683,7 +11276,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu la chambre. Elle a pris le seau. Le seau attend au pied du lit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10823,7 +11416,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le seau.
+narrateur|Le seau attend au pied du lit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10851,7 +11452,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de après la sieste, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou a chaud, sous le plaid. La sieste sent encore la chambre. Mila rejoint le doudou. On est dans la chambre, après la sieste. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10991,7 +11592,24 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de après la sieste, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou a chaud, sous le plaid.
+narrateur|La sieste sent encore la chambre.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans la chambre, après la sieste.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11019,7 +11637,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, après la sieste. Elle a vu la chambre. Elle a pris le doudou. Le plaid recouvre le doudou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11159,7 +11777,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, après la sieste.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le doudou.
+narrateur|Le plaid recouvre le doudou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11187,7 +11813,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le soir. Ça sent le pain chaud. maman sourit. Ici, c'est le soir. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tait une seconde. Je suis là. On reste ensemble.</t>
+          <t>C'est le soir, au marché. Les lampes sont jaunes, tout bas. Les ombres sont longues. Mila a froid aux mains. Elle veut parler. Elle lève la main. Elle attend. J'écoute les œufs d'abord. Puis c'est ton tour. Les lampes sont jaunes. Bravo. Tu as attendu. Puis tu as parlé. Le panier est lourd, tout plein. On lève la main. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11327,8 +11953,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Léa va vers le soir. Ça sent le pain chaud. maman sourit. Ici, c'est le soir. Ce n'est pas comme les autres endroits. Léa se souvient : attendre, puis parler. Voici le geste : lever la main ; attendre. On se tait une seconde.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|C'est le soir, au marché.
+narrateur|Les lampes sont jaunes, tout bas.
+narrateur|Les ombres sont longues.
+narrateur|Mila a froid aux mains.
+narrateur|Elle veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|J'écoute les œufs d'abord.
+maman|Puis c'est ton tour.
+enfant-f|Les lampes sont jaunes.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Le panier est lourd, tout plein.
+papa|On lève la main. On attend.
+enfant-f|Puis on parle.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11356,7 +11995,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Tour de parole.</t>
+          <t>On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11512,7 +12151,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Tour de parole.</t>
+          <t>narrateur|On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11540,7 +12179,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+          <t>Oui. On attend. Puis on parle. Mila hoche la tête. Bravo, Mila. Tu as fait du bon travail. Merci, maman.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11684,7 +12323,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : lever la main ; attendre. Léa respire. Léa retient : attendre, puis parler. On continue, avec maman.</t>
+          <t>narrateur|Oui.
+maman|On attend.
+papa|Puis on parle.
+narrateur|Mila hoche la tête.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+enfant-f|Merci, maman.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11712,7 +12357,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>On rentre où, maintenant ? La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11876,7 +12521,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|On rentre où, maintenant ?
+papa|La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11904,7 +12550,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi la cuisine. La lumière est claire. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+          <t>Mila a choisi la cuisine, le soir. Ça sent le pain chaud. La table est un peu farinée. Mila veut parler. Elle lève la main. Elle attend. Je parle du pain d'abord. Puis c'est toi, Mila. Le pain est chaud. Bravo. Tu as attendu. Puis tu as parlé. Une miette brille sur le bois. On lève la main, même à table. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12044,7 +12690,20 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi la cuisine. La lumière est claire. La cuisine reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On se tient la main. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi la cuisine, le soir.
+narrateur|Ça sent le pain chaud.
+narrateur|La table est un peu farinée.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|Je parle du pain d'abord.
+maman|Puis c'est toi, Mila.
+enfant-f|Le pain est chaud.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Une miette brille sur le bois.
+papa|On lève la main, même à table.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12072,7 +12731,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12236,7 +12895,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12264,7 +12924,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le soir, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon brille sous la lampe. La cuisine est jaune, tout doux. Mila rejoint le ballon. On est dans la cuisine, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12404,7 +13064,24 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le soir, la cuisine et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon brille sous la lampe.
+narrateur|La cuisine est jaune, tout doux.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans la cuisine, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12432,7 +13109,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu la cuisine. Elle a pris le ballon. La lampe pose un rond sur le ballon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12572,7 +13249,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le ballon.
+narrateur|La lampe pose un rond sur le ballon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12600,7 +13285,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. La lumière est claire. On se tient la main. Cette fin-là est celle de le soir, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau pose près de la soupe. La vapeur fait un nuage. Mila rejoint le seau. On est dans la cuisine, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12740,7 +13425,24 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. La lumière est claire. On se tient la main. Cette fin-là est celle de le soir, la cuisine et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau pose près de la soupe.
+narrateur|La vapeur fait un nuage.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans la cuisine, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12768,7 +13470,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu la cuisine. Elle a pris le seau. La vapeur a quitté le seau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12908,7 +13610,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le seau.
+narrateur|La vapeur a quitté le seau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12936,7 +13646,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le soir, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou a une miette sur l'oreille. La tasse de papa fume. Mila rejoint le doudou. On est dans la cuisine, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13076,7 +13786,24 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le soir, la cuisine et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou a une miette sur l'oreille.
+narrateur|La tasse de papa fume.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans la cuisine, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13104,7 +13831,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu la cuisine. Elle a pris le doudou. La miette a quitté le doudou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13244,7 +13971,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu la cuisine.
+narrateur|Elle a pris le doudou.
+narrateur|La miette a quitté le doudou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13272,7 +14007,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le jardin. Il y a des miettes sur la table. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+          <t>Mila a choisi le jardin, le soir. Le vent est doux, un peu frais. Une feuille tourne, tout lent. Mila veut parler. Elle lève la main. Elle attend. Je parle du vent d'abord. Ensuite, c'est toi. La feuille tourne. Bravo, Mila. Tu as attendu. Puis parlé. L'herbe est un peu mouillée. On lève la main, même dehors. Puis on parle.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13412,7 +14147,20 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi le jardin. Il y a des miettes sur la table. Le jardin reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On range un objet. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi le jardin, le soir.
+narrateur|Le vent est doux, un peu frais.
+narrateur|Une feuille tourne, tout lent.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maman|Je parle du vent d'abord.
+papa|Ensuite, c'est toi.
+enfant-f|La feuille tourne.
+maman|Bravo, Mila.
+papa|Tu as attendu. Puis parlé.
+narrateur|L'herbe est un peu mouillée.
+maman|On lève la main, même dehors.
+enfant-f|Puis on parle.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13440,7 +14188,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13604,7 +14352,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13632,7 +14381,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le soir, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon se cache dans l'ombre du soir. Un grillon chante, tout loin. Mila rejoint le ballon. On est dans le jardin, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13772,7 +14521,24 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le soir, le jardin et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon se cache dans l'ombre du soir.
+narrateur|Un grillon chante, tout loin.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans le jardin, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13800,7 +14566,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu le jardin. Elle a pris le ballon. Le grillon s'est tu, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13940,7 +14706,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le ballon.
+narrateur|Le grillon s'est tu, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13968,7 +14742,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le soir, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau est froid, le soir. La terre du jardin sent fort. Mila rejoint le seau. On est dans le jardin, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14108,7 +14882,24 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le soir, le jardin et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau est froid, le soir.
+narrateur|La terre du jardin sent fort.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans le jardin, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14136,7 +14927,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu le jardin. Elle a pris le seau. Le seau a de la terre au fond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14276,7 +15067,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le seau.
+narrateur|Le seau a de la terre au fond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14304,7 +15103,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le soir, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou rentre du jardin, tout sage. Une étoile apparaît, tout petit. Mila rejoint le doudou. On est dans le jardin, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14444,7 +15243,24 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le soir, le jardin et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou rentre du jardin, tout sage.
+narrateur|Une étoile apparaît, tout petit.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans le jardin, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14472,7 +15288,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu le jardin. Elle a pris le doudou. Une étoile reste à la fenêtre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14612,7 +15428,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu le jardin.
+narrateur|Elle a pris le doudou.
+narrateur|Une étoile reste à la fenêtre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14640,7 +15464,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi la chambre. Un chat miaule une fois. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+          <t>Mila a choisi la chambre, le soir. Le plaid est doux, tout chaud. La lampe fait un rond jaune. Mila veut parler. Elle lève la main. Elle attend. Je parle de la lampe d'abord. Puis c'est ton tour. Le plaid est doux. Bravo. Tu as attendu. Puis tu as parlé. Le doudou attend sur l'oreiller. On lève la main, même ici. J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14780,7 +15604,20 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi la chambre. Un chat miaule une fois. La chambre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : lever la main ; attendre. Léa répète tout bas : attendre, puis parler. On dit merci. papa n'est pas loin.</t>
+          <t>narrateur|Mila a choisi la chambre, le soir.
+narrateur|Le plaid est doux, tout chaud.
+narrateur|La lampe fait un rond jaune.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|Je parle de la lampe d'abord.
+maman|Puis c'est ton tour.
+enfant-f|Le plaid est doux.
+papa|Bravo. Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Le doudou attend sur l'oreiller.
+papa|On lève la main, même ici.
+enfant-f|J'attends. Puis je parle.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14808,7 +15645,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On prend quel jouet ? Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14972,7 +15809,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On prend quel jouet ?
+maman|Le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15000,7 +15838,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le ballon. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le soir, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le ballon roule vers la lampe. Le soir est calme, dans la chambre. Mila rejoint le ballon. On est dans la chambre, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15140,7 +15978,24 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le ballon. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le soir, la chambre et le ballon. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le ballon roule vers la lampe.
+narrateur|Le soir est calme, dans la chambre.
+narrateur|Mila rejoint le ballon.
+narrateur|On est dans la chambre, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15168,7 +16023,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu la chambre. Elle a pris le ballon. Le ballon est jaune, sous la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15308,7 +16163,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le ballon.
+narrateur|Le ballon est jaune, sous la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15336,7 +16199,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le seau. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le soir, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le seau rentre sous le lit. La lampe fait un rond sur le bois. Mila rejoint le seau. On est dans la chambre, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15476,7 +16339,24 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le seau. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le soir, la chambre et le seau. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le seau rentre sous le lit.
+narrateur|La lampe fait un rond sur le bois.
+narrateur|Mila rejoint le seau.
+narrateur|On est dans la chambre, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15504,7 +16384,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu la chambre. Elle a pris le seau. Le seau a disparu sous le lit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15644,7 +16524,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le seau.
+narrateur|Le seau a disparu sous le lit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15672,7 +16560,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le doudou. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le soir, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>Le doudou ferme les yeux, presque. Le plaid sent encore le marché. Mila rejoint le doudou. On est dans la chambre, le soir. Mila veut parler. Elle lève la main. Elle attend. C'est ton tour, Mila. J'ai levé la main. J'ai attendu. Puis j'ai parlé. Bravo, Mila. Tu as fait du bon travail. On lève la main. On attend. Puis on parle. Merci, maman. Merci, papa. Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15812,7 +16700,24 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le doudou. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le soir, la chambre et le doudou. Léa a appris : Tour de parole. Voici le geste : lever la main ; attendre. Léa a entendu : attendre, puis parler. Léa dit merci à maman. On rentre.</t>
+          <t>narrateur|Le doudou ferme les yeux, presque.
+narrateur|Le plaid sent encore le marché.
+narrateur|Mila rejoint le doudou.
+narrateur|On est dans la chambre, le soir.
+narrateur|Mila veut parler.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour, Mila.
+enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu.
+enfant-f|Puis j'ai parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|On lève la main. On attend.
+papa|Puis on parle.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le panier du marché repose, tout plein.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15840,7 +16745,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai levé la main. J'ai attendu. Puis parlé. Bravo, Mila. Tu as fait du bon travail. Mila est allée au marché, le soir. Elle a vu la chambre. Elle a pris le doudou. Le doudou sent encore les oranges. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15980,7 +16885,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai levé la main.
+enfant-f|J'ai attendu. Puis parlé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila est allée au marché, le soir.
+narrateur|Elle a vu la chambre.
+narrateur|Elle a pris le doudou.
+narrateur|Le doudou sent encore les oranges.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16002,7 +16915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16040,6 +16953,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-010.xlsx
+++ b/stories/arbres/TREE-COL-010.xlsx
@@ -2734,17 +2734,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mila pose une seule orange. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
+          <t>Mila pose une seule orange. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose une seule &lt;emphasis level="moderate"&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose une seule &lt;emphasis level="moderate"&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Mila pose une seule &lt;emphasis&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
+          <t>Mila pose une seule &lt;emphasis&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
 papa|On peut en ajouter.
 enfant-f|Celle-là aussi.
 narrateur|Les autres suivent, une par une.
-maman|Chaque clic a eu sa place.
+maman|Le clic est net, cette fois.
 narrateur|Les oranges rejoignent le petit panier.
 enfant-f|Il n'est plus vide.</t>
         </is>
@@ -3484,17 +3484,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le plateau reste collant de pomme. Mila prend le torchon rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
+          <t>Le plateau reste collant de pomme. Mila prend le torchon rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le plateau reste collant de pomme. Mila prend le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le plateau reste collant de pomme. Mila prend le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le plateau reste collant de pomme. Mila prend le &lt;emphasis&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
+          <t>Le plateau reste collant de pomme. Mila prend le &lt;emphasis&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3632,7 +3632,7 @@
 narrateur|Mila prend le torchon rayé.
 narrateur|Papa approche une orange trop vite.
 enfant-f|Pas maintenant.
-narrateur|Elle essuie, puis elle attend.
+narrateur|Elle essuie, puis elle regarde.
 narrateur|Le métal redevient mat.
 enfant-f|C'est sec.
 papa|On pose les oranges.
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'orange du fond trône dans le panier. Les autres attendent près de l'évier. Celle-là, d'abord. Tu l'as demandée au bon silence. Le jus de celle du fond est plus pâle. On la reconnaît ? Oui. Elle était cachée. Une écharde de caisse reste dans l'osier. L'orange du fond brille toute seule.</t>
+          <t>L'orange du fond trône dans le panier. Les autres attendent près de l'évier. Celle-là, d'abord. Tu l'as dite après le thym. Le jus de celle du fond est plus pâle. On la reconnaît ? Oui. Elle était cachée. Une écharde de caisse reste dans l'osier. L'orange du fond brille toute seule.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'orange du fond trône dans le panier. Les autres attendent près de l'évier. Celle-là, d'abord. Tu l'as demandée au bon silence. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; de celle du fond est plus pâle. On la reconnaît ? Oui. Elle était cachée. Une écharde de caisse reste dans l'osier. L'orange du fond brille toute seule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'orange du fond trône dans le panier. Les autres attendent près de l'évier. Celle-là, d'abord. Tu l'as dite après le thym. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; de celle du fond est plus pâle. On la reconnaît ? Oui. Elle était cachée. Une écharde de caisse reste dans l'osier. L'orange du fond brille toute seule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'orange du fond trône dans le panier. Les autres attendent près de l'évier. Celle-là, d'abord. Tu l'as demandée au bon silence. Le &lt;emphasis&gt;jus&lt;/emphasis&gt; de celle du fond est plus pâle. On la reconnaît ? Oui. Elle était cachée. Une écharde de caisse reste dans l'osier. L'orange du fond brille toute seule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'orange du fond trône dans le panier. Les autres attendent près de l'évier. Celle-là, d'abord. Tu l'as dite après le thym. Le &lt;emphasis&gt;jus&lt;/emphasis&gt; de celle du fond est plus pâle. On la reconnaît ? Oui. Elle était cachée. Une écharde de caisse reste dans l'osier. L'orange du fond brille toute seule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
           <t>narrateur|L'orange du fond trône dans le panier.
 narrateur|Les autres attendent près de l'évier.
 enfant-f|Celle-là, d'abord.
-maman|Tu l'as demandée au bon silence.
+maman|Tu l'as dite après le thym.
 narrateur|Le jus de celle du fond est plus pâle.
 papa|On la reconnaît ?
 enfant-f|Oui.
@@ -4623,17 +4623,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>La marchande ramasse un tas. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
+          <t>La marchande ramasse un tas. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La marchande ramasse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La marchande ramasse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>La marchande ramasse un &lt;emphasis&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
+          <t>La marchande ramasse un &lt;emphasis&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
 narrateur|Le compte se casse.
 narrateur|Elle remet le fruit dans la caisse.
 narrateur|Les nombres reprennent.
-enfant-f|J'attends la fin.
+enfant-f|Les nombres d'abord.
 papa|Le tas est le sien, maintenant.
 maman|Quatre, comme elle voulait.
 narrateur|Le bois de la caisse sent l'écorce.
@@ -5373,17 +5373,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le panier dans le chariot. La roue tient le tapis du stand. Papa tire, maman paie des fraises. Deux gestes en même temps. Le panier glisse vers le bord. Mila l'attrape, sans crier. Maman range la monnaie. Le panier allait tomber. On recule le chariot, alors. La roue quitte le tapis. La balance reparaît. Tu as parlé au bon moment.</t>
+          <t>Mila pose le panier dans le chariot. La roue tient le tapis du stand. Papa tire, maman paie des fraises. Deux gestes en même temps. Le panier glisse vers le bord. Mila l'attrape, sans crier. Maman range la monnaie. Le panier allait tomber. On recule le chariot, alors. La roue quitte le tapis. La balance reparaît. On voit la balance.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila pose le panier dans le &lt;emphasis level="moderate"&gt;chariot&lt;/emphasis&gt;. La roue tient le tapis du stand. Papa tire, maman paie des fraises. Deux gestes en même temps. Le panier glisse vers le bord. Mila l'attrape, sans crier. Maman range la monnaie. Le panier allait tomber. On recule le chariot, alors. La roue quitte le tapis. La balance reparaît. Tu as parlé au bon moment.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Mila pose le panier dans le &lt;emphasis level="moderate"&gt;chariot&lt;/emphasis&gt;. La roue tient le tapis du stand. Papa tire, maman paie des fraises. Deux gestes en même temps. Le panier glisse vers le bord. Mila l'attrape, sans crier. Maman range la monnaie. Le panier allait tomber. On recule le chariot, alors. La roue quitte le tapis. La balance reparaît. On voit la balance.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Mila pose le panier dans le &lt;emphasis&gt;chariot&lt;/emphasis&gt;. La roue tient le tapis du stand. Papa tire, maman paie des fraises. Deux gestes en même temps. Le panier glisse vers le bord. Mila l'attrape, sans crier. Maman range la monnaie. Le panier allait tomber. On recule le chariot, alors. La roue quitte le tapis. La balance reparaît. Tu as parlé au bon moment.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Mila pose le panier dans le &lt;emphasis&gt;chariot&lt;/emphasis&gt;. La roue tient le tapis du stand. Papa tire, maman paie des fraises. Deux gestes en même temps. Le panier glisse vers le bord. Mila l'attrape, sans crier. Maman range la monnaie. Le panier allait tomber. On recule le chariot, alors. La roue quitte le tapis. La balance reparaît. On voit la balance.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
 papa|On recule le chariot, alors.
 narrateur|La roue quitte le tapis.
 narrateur|La balance reparaît.
-maman|Tu as parlé au bon moment.</t>
+maman|On voit la balance.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -5948,17 +5948,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Le panier a voyagé dans le chariot. Il pose près de la fenêtre. La première orange n'a pas bougé. Elle s'est calée, toute seule. J'ai attendu qu'elle s'arrête. Le jus de celle-là, pour toi. Dehors, une roue lointaine se tait. Mila boit, les yeux sur le panier. Dans l'osier, la première orange tient.</t>
+          <t>Le panier a voyagé dans le chariot. Il pose près de la fenêtre. La première orange n'a pas bougé. Elle s'est calée, toute seule. Elle ne roulait plus. Le jus de celle-là, pour toi. Dehors, une roue lointaine se tait. Mila boit, les yeux sur le panier. Dans l'osier, la première orange tient.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le panier a voyagé dans le chariot. Il pose près de la fenêtre. La première orange n'a pas bougé. Elle s'est calée, toute seule. J'ai attendu qu'elle s'arrête. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; de celle-là, pour toi. Dehors, une roue lointaine se tait. Mila boit, les yeux sur le panier. Dans l'osier, la première orange tient.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le panier a voyagé dans le chariot. Il pose près de la fenêtre. La première orange n'a pas bougé. Elle s'est calée, toute seule. Elle ne roulait plus. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; de celle-là, pour toi. Dehors, une roue lointaine se tait. Mila boit, les yeux sur le panier. Dans l'osier, la première orange tient.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le panier a voyagé dans le chariot. Il pose près de la fenêtre. La première orange n'a pas bougé. Elle s'est calée, toute seule. J'ai attendu qu'elle s'arrête. Le &lt;emphasis&gt;jus&lt;/emphasis&gt; de celle-là, pour toi. Dehors, une roue lointaine se tait. Mila boit, les yeux sur le panier. Dans l'osier, la première orange tient.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le panier a voyagé dans le chariot. Il pose près de la fenêtre. La première orange n'a pas bougé. Elle s'est calée, toute seule. Elle ne roulait plus. Le &lt;emphasis&gt;jus&lt;/emphasis&gt; de celle-là, pour toi. Dehors, une roue lointaine se tait. Mila boit, les yeux sur le panier. Dans l'osier, la première orange tient.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6100,7 +6100,7 @@
 narrateur|Il pose près de la fenêtre.
 narrateur|La première orange n'a pas bougé.
 papa|Elle s'est calée, toute seule.
-enfant-f|J'ai attendu qu'elle s'arrête.
+enfant-f|Elle ne roulait plus.
 maman|Le jus de celle-là, pour toi.
 narrateur|Dehors, une roue lointaine se tait.
 narrateur|Mila boit, les yeux sur le panier.
@@ -6136,17 +6136,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Mila verse un tas dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
+          <t>Mila verse un tas dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila verse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila verse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Mila verse un &lt;emphasis&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
+          <t>Mila verse un &lt;emphasis&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6285,7 +6285,7 @@
 enfant-f|Elles partent !
 narrateur|Papa parle du chemin du retour.
 narrateur|Il n'a pas vu la roue.
-narrateur|Mila attend sa fin de phrase.
+narrateur|Mila laisse papa finir.
 enfant-f|Le tas va vers la roue.
 papa|On les recule, alors.
 narrateur|Le tas se cale contre le bois.
@@ -6512,17 +6512,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le fond du chariot porte du sable. Mila essuie avec le torchon. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
+          <t>Le fond du chariot porte du sable. Mila essuie avec le torchon. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges rejoignent le petit panier. Il n'est plus vide.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges rejoignent le petit panier. Il n'est plus vide.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
+          <t>Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges rejoignent le petit panier. Il n'est plus vide. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6664,7 +6664,7 @@
 narrateur|Papa n'entend pas, il charge.
 narrateur|Mila montre le torchon sale.
 papa|Pardon.
-papa|J'attendais pas.
+papa|Je chargeais trop vite.
 narrateur|Elle finit le fond, toute seule.
 maman|Les oranges peuvent entrer, là.
 narrateur|Les oranges rejoignent le petit panier.
@@ -8031,17 +8031,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Mila pose une seule orange. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Les oranges glissent dans le filet. Les mailles tiennent.</t>
+          <t>Mila pose une seule orange. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Les oranges glissent dans le filet. Les mailles tiennent.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose une seule &lt;emphasis level="moderate"&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose une seule &lt;emphasis level="moderate"&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Mila pose une seule &lt;emphasis&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
+          <t>Mila pose une seule &lt;emphasis&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8184,7 +8184,7 @@
 papa|On peut en ajouter.
 enfant-f|Celle-là aussi.
 narrateur|Les autres suivent, une par une.
-maman|Chaque clic a eu sa place.
+maman|Le clic est net, cette fois.
 narrateur|Les oranges glissent dans le filet.
 enfant-f|Les mailles tiennent.</t>
         </is>
@@ -8781,17 +8781,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le plateau reste collant de pomme. Mila prend le torchon rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges glissent dans le filet. Les mailles tiennent.</t>
+          <t>Le plateau reste collant de pomme. Mila prend le torchon rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges glissent dans le filet. Les mailles tiennent.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le plateau reste collant de pomme. Mila prend le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le plateau reste collant de pomme. Mila prend le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Le plateau reste collant de pomme. Mila prend le &lt;emphasis&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
+          <t>Le plateau reste collant de pomme. Mila prend le &lt;emphasis&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
 narrateur|Mila prend le torchon rayé.
 narrateur|Papa approche une orange trop vite.
 enfant-f|Pas maintenant.
-narrateur|Elle essuie, puis elle attend.
+narrateur|Elle essuie, puis elle regarde.
 narrateur|Le métal redevient mat.
 enfant-f|C'est sec.
 papa|On pose les oranges.
@@ -9156,17 +9156,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Une maille du filet pince une latte. Mila tire, la caisse crisse. La marchande décrit le thym à maman. Il est coincé ! Les deux voix couvrent la sienne. Mila lâche la maille. Elle attend la fin des mots. Le thym est choisi. La marchande se tait. Le filet tenait la caisse. On le détache ensemble. L'orange du fond apparaît.</t>
+          <t>Une maille du filet pince une latte. Mila tire, la caisse crisse. La marchande décrit le thym à maman. Il est coincé ! Les deux voix couvrent la sienne. Mila lâche la maille. Les mots de thym s'arrêtent. Le thym est choisi. La marchande se tait. Le filet tenait la caisse. On le détache ensemble. L'orange du fond apparaît.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une maille du filet pince une latte. Mila tire, la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt; crisse. La marchande décrit le thym à maman. Il est coincé ! Les deux voix couvrent la sienne. Mila lâche la maille. Elle attend la fin des mots. Le thym est choisi. La marchande se tait. Le filet tenait la caisse. On le détache ensemble. L'orange du fond apparaît.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Une maille du filet pince une latte. Mila tire, la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt; crisse. La marchande décrit le thym à maman. Il est coincé ! Les deux voix couvrent la sienne. Mila lâche la maille. Les mots de thym s'arrêtent. Le thym est choisi. La marchande se tait. Le filet tenait la caisse. On le détache ensemble. L'orange du fond apparaît.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Une maille du filet pince une latte. Mila tire, la &lt;emphasis&gt;caisse&lt;/emphasis&gt; crisse. La marchande décrit le thym à maman. Il est coincé ! Les deux voix couvrent la sienne. Mila lâche la maille. Elle attend la fin des mots. Le thym est choisi. La marchande se tait. Le filet tenait la caisse. On le détache ensemble. L'orange du fond apparaît.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Une maille du filet pince une latte. Mila tire, la &lt;emphasis&gt;caisse&lt;/emphasis&gt; crisse. La marchande décrit le thym à maman. Il est coincé ! Les deux voix couvrent la sienne. Mila lâche la maille. Les mots de thym s'arrêtent. Le thym est choisi. La marchande se tait. Le filet tenait la caisse. On le détache ensemble. L'orange du fond apparaît.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -9310,7 +9310,7 @@
 enfant-f|Il est coincé !
 narrateur|Les deux voix couvrent la sienne.
 narrateur|Mila lâche la maille.
-narrateur|Elle attend la fin des mots.
+narrateur|Les mots de thym s'arrêtent.
 narrateur|Le thym est choisi.
 narrateur|La marchande se tait.
 enfant-f|Le filet tenait la caisse.
@@ -9920,17 +9920,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>La marchande ramasse un tas. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges glissent dans le filet. Les mailles tiennent.</t>
+          <t>La marchande ramasse un tas. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges glissent dans le filet. Les mailles tiennent.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La marchande ramasse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La marchande ramasse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>La marchande ramasse un &lt;emphasis&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
+          <t>La marchande ramasse un &lt;emphasis&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
 narrateur|Le compte se casse.
 narrateur|Elle remet le fruit dans la caisse.
 narrateur|Les nombres reprennent.
-enfant-f|J'attends la fin.
+enfant-f|Les nombres d'abord.
 papa|Le tas est le sien, maintenant.
 maman|Quatre, comme elle voulait.
 narrateur|Le bois de la caisse sent l'écorce.
@@ -11245,17 +11245,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Le filet repose sur le rebord du chariot. Le chariot est rentré dans la cour. Mila prend la première orange. Celle qui ne roulait plus. J'ai attendu le choc. Le jus, sur le pas ? Ils s'assoient sur la pierre froide. Le filet pend dans la lumière. La première orange a un goût de vent.</t>
+          <t>Le filet repose sur le rebord du chariot. Le chariot est rentré dans la cour. Mila prend la première orange. Celle qui ne roulait plus. Le choc, puis plus rien. Le jus, sur le pas ? Ils s'assoient sur la pierre froide. Le filet pend dans la lumière. La première orange a un goût de vent.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le filet repose sur le rebord du chariot. Le chariot est rentré dans la cour. Mila prend la première orange. Celle qui ne roulait plus. J'ai attendu le choc. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt;, sur le pas ? Ils s'assoient sur la pierre froide. Le filet pend dans la lumière. La première orange a un goût de vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le filet repose sur le rebord du chariot. Le chariot est rentré dans la cour. Mila prend la première orange. Celle qui ne roulait plus. Le choc, puis plus rien. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt;, sur le pas ? Ils s'assoient sur la pierre froide. Le filet pend dans la lumière. La première orange a un goût de vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le filet repose sur le rebord du chariot. Le chariot est rentré dans la cour. Mila prend la première orange. Celle qui ne roulait plus. J'ai attendu le choc. Le &lt;emphasis&gt;jus&lt;/emphasis&gt;, sur le pas ? Ils s'assoient sur la pierre froide. Le filet pend dans la lumière. La première orange a un goût de vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le filet repose sur le rebord du chariot. Le chariot est rentré dans la cour. Mila prend la première orange. Celle qui ne roulait plus. Le choc, puis plus rien. Le &lt;emphasis&gt;jus&lt;/emphasis&gt;, sur le pas ? Ils s'assoient sur la pierre froide. Le filet pend dans la lumière. La première orange a un goût de vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11397,7 +11397,7 @@
 narrateur|Le chariot est rentré dans la cour.
 narrateur|Mila prend la première orange.
 papa|Celle qui ne roulait plus.
-enfant-f|J'ai attendu le choc.
+enfant-f|Le choc, puis plus rien.
 maman|Le jus, sur le pas ?
 narrateur|Ils s'assoient sur la pierre froide.
 narrateur|Le filet pend dans la lumière.
@@ -11433,17 +11433,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Mila verse un tas dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges glissent dans le filet. Les mailles tiennent.</t>
+          <t>Mila verse un tas dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges glissent dans le filet. Les mailles tiennent.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila verse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila verse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Mila verse un &lt;emphasis&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
+          <t>Mila verse un &lt;emphasis&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11582,7 +11582,7 @@
 enfant-f|Elles partent !
 narrateur|Papa parle du chemin du retour.
 narrateur|Il n'a pas vu la roue.
-narrateur|Mila attend sa fin de phrase.
+narrateur|Mila laisse papa finir.
 enfant-f|Le tas va vers la roue.
 papa|On les recule, alors.
 narrateur|Le tas se cale contre le bois.
@@ -11808,17 +11808,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le fond du chariot porte du sable. Mila essuie avec le torchon. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges glissent dans le filet. Les mailles tiennent.</t>
+          <t>Le fond du chariot porte du sable. Mila essuie avec le torchon. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges glissent dans le filet. Les mailles tiennent.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges glissent dans le filet. Les mailles tiennent.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
+          <t>Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Les oranges glissent dans le filet. Les mailles tiennent. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11960,7 +11960,7 @@
 narrateur|Papa n'entend pas, il charge.
 narrateur|Mila montre le torchon sale.
 papa|Pardon.
-papa|J'attendais pas.
+papa|Je chargeais trop vite.
 narrateur|Elle finit le fond, toute seule.
 maman|Les oranges peuvent entrer, là.
 narrateur|Les oranges glissent dans le filet.
@@ -13325,17 +13325,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Mila pose une seule orange. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
+          <t>Mila pose une seule orange. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose une seule &lt;emphasis level="moderate"&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose une seule &lt;emphasis level="moderate"&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Mila pose une seule &lt;emphasis&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Chaque clic a eu sa place. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
+          <t>Mila pose une seule &lt;emphasis&gt;orange&lt;/emphasis&gt;. Sa main revient avec une deuxième. L'aiguille n'a pas fini de bouger. Elle retire la deuxième orange. La balance fait clic. L'aiguille s'arrête. On peut en ajouter. Celle-là aussi. Les autres suivent, une par une. Le clic est net, cette fois. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
 papa|On peut en ajouter.
 enfant-f|Celle-là aussi.
 narrateur|Les autres suivent, une par une.
-maman|Chaque clic a eu sa place.
+maman|Le clic est net, cette fois.
 narrateur|Mila tend la pièce, sans la secouer.
 enfant-f|Pour les oranges rondes.</t>
         </is>
@@ -14076,17 +14076,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le plateau reste collant de pomme. Mila prend le torchon rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
+          <t>Le plateau reste collant de pomme. Mila prend le torchon rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le plateau reste collant de pomme. Mila prend le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le plateau reste collant de pomme. Mila prend le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Le plateau reste collant de pomme. Mila prend le &lt;emphasis&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle attend. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
+          <t>Le plateau reste collant de pomme. Mila prend le &lt;emphasis&gt;torchon&lt;/emphasis&gt; rayé. Papa approche une orange trop vite. Pas maintenant. Elle essuie, puis elle regarde. Le métal redevient mat. C'est sec. On pose les oranges. Le premier clic sonne net. Le torchon a rendu le plateau. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14224,7 +14224,7 @@
 narrateur|Mila prend le torchon rayé.
 narrateur|Papa approche une orange trop vite.
 enfant-f|Pas maintenant.
-narrateur|Elle essuie, puis elle attend.
+narrateur|Elle essuie, puis elle regarde.
 narrateur|Le métal redevient mat.
 enfant-f|C'est sec.
 papa|On pose les oranges.
@@ -14263,17 +14263,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>La pièce sèche sur le torchon rayé. Mila presse, les doigts propres. Plus de pomme, plus de collant. J'ai dit : pas maintenant. Le métal a attendu, lui aussi. Le jus tombe dans un bol à fleurs. La pièce ne glisse plus. Une rayure du torchon brille, humide. Le bol sent l'orange chaude.</t>
+          <t>La pièce sèche sur le torchon rayé. Mila presse, les doigts propres. Plus de pomme, plus de collant. J'ai dit : pas maintenant. Le métal était prêt, lui aussi. Le jus tombe dans un bol à fleurs. La pièce ne glisse plus. Une rayure du torchon brille, humide. Le bol sent l'orange chaude.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La pièce sèche sur le torchon rayé. Mila presse, les doigts propres. Plus de pomme, plus de collant. J'ai dit : pas maintenant. Le métal a attendu, lui aussi. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; tombe dans un bol à fleurs. La pièce ne glisse plus. Une rayure du torchon brille, humide. Le bol sent l'orange chaude.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La pièce sèche sur le torchon rayé. Mila presse, les doigts propres. Plus de pomme, plus de collant. J'ai dit : pas maintenant. Le métal était prêt, lui aussi. Le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; tombe dans un bol à fleurs. La pièce ne glisse plus. Une rayure du torchon brille, humide. Le bol sent l'orange chaude.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La pièce sèche sur le torchon rayé. Mila presse, les doigts propres. Plus de pomme, plus de collant. J'ai dit : pas maintenant. Le métal a attendu, lui aussi. Le &lt;emphasis&gt;jus&lt;/emphasis&gt; tombe dans un bol à fleurs. La pièce ne glisse plus. Une rayure du torchon brille, humide. Le bol sent l'orange chaude.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La pièce sèche sur le torchon rayé. Mila presse, les doigts propres. Plus de pomme, plus de collant. J'ai dit : pas maintenant. Le métal était prêt, lui aussi. Le &lt;emphasis&gt;jus&lt;/emphasis&gt; tombe dans un bol à fleurs. La pièce ne glisse plus. Une rayure du torchon brille, humide. Le bol sent l'orange chaude.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14415,7 +14415,7 @@
 narrateur|Mila presse, les doigts propres.
 papa|Plus de pomme, plus de collant.
 enfant-f|J'ai dit : pas maintenant.
-maman|Le métal a attendu, lui aussi.
+maman|Le métal était prêt, lui aussi.
 narrateur|Le jus tombe dans un bol à fleurs.
 narrateur|La pièce ne glisse plus.
 narrateur|Une rayure du torchon brille, humide.
@@ -15214,17 +15214,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>La marchande ramasse un tas. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
+          <t>La marchande ramasse un tas. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La marchande ramasse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La marchande ramasse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>La marchande ramasse un &lt;emphasis&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. J'attends la fin. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
+          <t>La marchande ramasse un &lt;emphasis&gt;tas&lt;/emphasis&gt;. Elle compte à voix haute. Mila ajoute une orange au milieu. Le compte se casse. Elle remet le fruit dans la caisse. Les nombres reprennent. Les nombres d'abord. Le tas est le sien, maintenant. Quatre, comme elle voulait. Le bois de la caisse sent l'écorce. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15364,7 +15364,7 @@
 narrateur|Le compte se casse.
 narrateur|Elle remet le fruit dans la caisse.
 narrateur|Les nombres reprennent.
-enfant-f|J'attends la fin.
+enfant-f|Les nombres d'abord.
 papa|Le tas est le sien, maintenant.
 maman|Quatre, comme elle voulait.
 narrateur|Le bois de la caisse sent l'écorce.
@@ -15965,17 +15965,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La pièce roule sous le chariot. Elle est dessous ! Papa veut pousser pour chercher. Maman tend l'argent des fraises. La roue pourrait bouger. Mila recule les mains. Elle attend la monnaie rangée. La pièce est sous le chariot. On ne touche pas la roue. Il se baisse, le chariot immobile. La pièce reparaît, un peu poussiéreuse. Merci d'avoir attendu le moment.</t>
+          <t>La pièce roule sous le chariot. Elle est dessous ! Papa veut pousser pour chercher. Maman tend l'argent des fraises. La roue pourrait bouger. Mila recule les mains. La monnaie rejoint la poche. La pièce est sous le chariot. On ne touche pas la roue. Il se baisse, le chariot immobile. La pièce reparaît, un peu poussiéreuse. Merci, la pièce est là.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;La pièce roule sous le &lt;emphasis level="moderate"&gt;chariot&lt;/emphasis&gt;. Elle est dessous ! Papa veut pousser pour chercher. Maman tend l'argent des fraises. La roue pourrait bouger. Mila recule les mains. Elle attend la monnaie rangée. La pièce est sous le chariot. On ne touche pas la roue. Il se baisse, le chariot immobile. La pièce reparaît, un peu poussiéreuse. Merci d'avoir attendu le moment.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;La pièce roule sous le &lt;emphasis level="moderate"&gt;chariot&lt;/emphasis&gt;. Elle est dessous ! Papa veut pousser pour chercher. Maman tend l'argent des fraises. La roue pourrait bouger. Mila recule les mains. La monnaie rejoint la poche. La pièce est sous le chariot. On ne touche pas la roue. Il se baisse, le chariot immobile. La pièce reparaît, un peu poussiéreuse. Merci, la pièce est là.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;La pièce roule sous le &lt;emphasis&gt;chariot&lt;/emphasis&gt;. Elle est dessous ! Papa veut pousser pour chercher. Maman tend l'argent des fraises. La roue pourrait bouger. Mila recule les mains. Elle attend la monnaie rangée. La pièce est sous le chariot. On ne touche pas la roue. Il se baisse, le chariot immobile. La pièce reparaît, un peu poussiéreuse. Merci d'avoir attendu le moment.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;La pièce roule sous le &lt;emphasis&gt;chariot&lt;/emphasis&gt;. Elle est dessous ! Papa veut pousser pour chercher. Maman tend l'argent des fraises. La roue pourrait bouger. Mila recule les mains. La monnaie rejoint la poche. La pièce est sous le chariot. On ne touche pas la roue. Il se baisse, le chariot immobile. La pièce reparaît, un peu poussiéreuse. Merci, la pièce est là.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -16119,12 +16119,12 @@
 narrateur|Maman tend l'argent des fraises.
 narrateur|La roue pourrait bouger.
 narrateur|Mila recule les mains.
-narrateur|Elle attend la monnaie rangée.
+narrateur|La monnaie rejoint la poche.
 enfant-f|La pièce est sous le chariot.
 papa|On ne touche pas la roue.
 narrateur|Il se baisse, le chariot immobile.
 narrateur|La pièce reparaît, un peu poussiéreuse.
-maman|Merci d'avoir attendu le moment.</t>
+maman|Merci, la pièce est là.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -16728,17 +16728,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Mila verse un tas dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
+          <t>Mila verse un tas dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila verse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila verse un &lt;emphasis level="moderate"&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Mila verse un &lt;emphasis&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila attend sa fin de phrase. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
+          <t>Mila verse un &lt;emphasis&gt;tas&lt;/emphasis&gt; dans le chariot. Les oranges roulent vers la roue. Elles partent ! Papa parle du chemin du retour. Il n'a pas vu la roue. Mila laisse papa finir. Le tas va vers la roue. On les recule, alors. Le tas se cale contre le bois. Plus rien ne roule. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16877,7 +16877,7 @@
 enfant-f|Elles partent !
 narrateur|Papa parle du chemin du retour.
 narrateur|Il n'a pas vu la roue.
-narrateur|Mila attend sa fin de phrase.
+narrateur|Mila laisse papa finir.
 enfant-f|Le tas va vers la roue.
 papa|On les recule, alors.
 narrateur|Le tas se cale contre le bois.
@@ -16915,17 +16915,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Le tas cache la pièce au fond du bol. Mila verse le jus par-dessus. Elles allaient vers la roue. J'ai attendu ta phrase. On retrouve la pièce après ? Mila plonge deux doigts, puis sourit. Elle est là, collée. Ils la lavent sous l'eau froide. Le tas, lui, a fini en jus doré.</t>
+          <t>Le tas cache la pièce au fond du bol. Mila verse le jus par-dessus. Elles allaient vers la roue. Après tes mots, je l'ai dit. On retrouve la pièce après ? Mila plonge deux doigts, puis sourit. Elle est là, collée. Ils la lavent sous l'eau froide. Le tas, lui, a fini en jus doré.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tas cache la pièce au fond du bol. Mila verse le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; par-dessus. Elles allaient vers la roue. J'ai attendu ta phrase. On retrouve la pièce après ? Mila plonge deux doigts, puis sourit. Elle est là, collée. Ils la lavent sous l'eau froide. Le tas, lui, a fini en jus doré.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tas cache la pièce au fond du bol. Mila verse le &lt;emphasis level="moderate"&gt;jus&lt;/emphasis&gt; par-dessus. Elles allaient vers la roue. Après tes mots, je l'ai dit. On retrouve la pièce après ? Mila plonge deux doigts, puis sourit. Elle est là, collée. Ils la lavent sous l'eau froide. Le tas, lui, a fini en jus doré.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tas cache la pièce au fond du bol. Mila verse le &lt;emphasis&gt;jus&lt;/emphasis&gt; par-dessus. Elles allaient vers la roue. J'ai attendu ta phrase. On retrouve la pièce après ? Mila plonge deux doigts, puis sourit. Elle est là, collée. Ils la lavent sous l'eau froide. Le tas, lui, a fini en jus doré.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tas cache la pièce au fond du bol. Mila verse le &lt;emphasis&gt;jus&lt;/emphasis&gt; par-dessus. Elles allaient vers la roue. Après tes mots, je l'ai dit. On retrouve la pièce après ? Mila plonge deux doigts, puis sourit. Elle est là, collée. Ils la lavent sous l'eau froide. Le tas, lui, a fini en jus doré.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -17066,7 +17066,7 @@
           <t>narrateur|Le tas cache la pièce au fond du bol.
 narrateur|Mila verse le jus par-dessus.
 papa|Elles allaient vers la roue.
-enfant-f|J'ai attendu ta phrase.
+enfant-f|Après tes mots, je l'ai dit.
 maman|On retrouve la pièce après ?
 narrateur|Mila plonge deux doigts, puis sourit.
 enfant-f|Elle est là, collée.
@@ -17103,17 +17103,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le fond du chariot porte du sable. Mila essuie avec le torchon. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
+          <t>Le fond du chariot porte du sable. Mila essuie avec le torchon. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Mila tend la pièce, sans la secouer. Pour les oranges rondes.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis level="moderate"&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Mila tend la pièce, sans la secouer. Pour les oranges rondes.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. J'attendais pas. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
+          <t>Le fond du chariot porte du sable. Mila essuie avec le &lt;emphasis&gt;torchon&lt;/emphasis&gt;. Papa pose une orange trop tôt. Le fruit frotte le grain. Le sable. Papa n'entend pas, il charge. Mila montre le torchon sale. Pardon. Je chargeais trop vite. Elle finit le fond, toute seule. Les oranges peuvent entrer, là. Mila tend la pièce, sans la secouer. Pour les oranges rondes. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17255,7 +17255,7 @@
 narrateur|Papa n'entend pas, il charge.
 narrateur|Mila montre le torchon sale.
 papa|Pardon.
-papa|J'attendais pas.
+papa|Je chargeais trop vite.
 narrateur|Elle finit le fond, toute seule.
 maman|Les oranges peuvent entrer, là.
 narrateur|Mila tend la pièce, sans la secouer.
@@ -17473,7 +17473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17530,6 +17530,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
